--- a/artfynd/A 6679-2025 artfynd.xlsx
+++ b/artfynd/A 6679-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123401667</v>
+        <v>123407471</v>
       </c>
       <c r="B17" t="n">
-        <v>79389</v>
+        <v>78508</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,34 +2310,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>396252</v>
+        <v>396183</v>
       </c>
       <c r="R17" t="n">
-        <v>6845715</v>
+        <v>6845919</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123407258</v>
+        <v>123407713</v>
       </c>
       <c r="B18" t="n">
-        <v>79389</v>
+        <v>79360</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,21 +2422,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396137</v>
+        <v>396195</v>
       </c>
       <c r="R18" t="n">
-        <v>6845971</v>
+        <v>6845835</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123403134</v>
+        <v>123401667</v>
       </c>
       <c r="B19" t="n">
-        <v>78416</v>
+        <v>79389</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,34 +2534,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396200</v>
+        <v>396252</v>
       </c>
       <c r="R19" t="n">
-        <v>6845887</v>
+        <v>6845715</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123407432</v>
+        <v>123407258</v>
       </c>
       <c r="B20" t="n">
-        <v>56691</v>
+        <v>79389</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,43 +2642,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>396184</v>
+        <v>396137</v>
       </c>
       <c r="R20" t="n">
-        <v>6845920</v>
+        <v>6845971</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2710,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2720,7 +2715,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,10 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123407471</v>
+        <v>123403134</v>
       </c>
       <c r="B21" t="n">
-        <v>78508</v>
+        <v>78416</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,21 +2758,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2787,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>396183</v>
+        <v>396200</v>
       </c>
       <c r="R21" t="n">
-        <v>6845919</v>
+        <v>6845887</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2822,7 +2817,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2832,7 +2827,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,10 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123407713</v>
+        <v>123407432</v>
       </c>
       <c r="B22" t="n">
-        <v>79360</v>
+        <v>56691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,38 +2866,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>396195</v>
+        <v>396184</v>
       </c>
       <c r="R22" t="n">
-        <v>6845835</v>
+        <v>6845920</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2971,10 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123403728</v>
+        <v>123404245</v>
       </c>
       <c r="B23" t="n">
-        <v>78416</v>
+        <v>78508</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2987,34 +2987,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>396152</v>
+        <v>396199</v>
       </c>
       <c r="R23" t="n">
-        <v>6845999</v>
+        <v>6846035</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,22 +3061,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123404245</v>
+        <v>123403728</v>
       </c>
       <c r="B24" t="n">
-        <v>78508</v>
+        <v>78416</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3089,34 +3089,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>396199</v>
+        <v>396152</v>
       </c>
       <c r="R24" t="n">
-        <v>6846035</v>
+        <v>6845999</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123404309</v>
+        <v>123406080</v>
       </c>
       <c r="B32" t="n">
-        <v>78416</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3915,34 +3915,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396057</v>
+        <v>396199</v>
       </c>
       <c r="R32" t="n">
-        <v>6846006</v>
+        <v>6846035</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3989,22 +3994,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123407564</v>
+        <v>123404309</v>
       </c>
       <c r="B33" t="n">
-        <v>90977</v>
+        <v>78416</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,46 +4022,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>396154</v>
+        <v>396057</v>
       </c>
       <c r="R33" t="n">
-        <v>6845889</v>
+        <v>6846006</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4083,19 +4079,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,19 +4096,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123406704</v>
+        <v>123407564</v>
       </c>
       <c r="B34" t="n">
         <v>90977</v>
@@ -4155,20 +4141,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396147</v>
+        <v>396154</v>
       </c>
       <c r="R34" t="n">
-        <v>6845922</v>
+        <v>6845889</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4195,9 +4190,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4212,22 +4217,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123406080</v>
+        <v>123406704</v>
       </c>
       <c r="B35" t="n">
-        <v>57481</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,39 +4245,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396199</v>
+        <v>396147</v>
       </c>
       <c r="R35" t="n">
-        <v>6846035</v>
+        <v>6845922</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4319,12 +4319,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123402056</v>
+        <v>123407519</v>
       </c>
       <c r="B41" t="n">
-        <v>77699</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4886,37 +4886,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396287</v>
+        <v>396082</v>
       </c>
       <c r="R41" t="n">
-        <v>6845734</v>
+        <v>6845745</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4972,10 +4977,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123404225</v>
+        <v>123406774</v>
       </c>
       <c r="B42" t="n">
-        <v>78507</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4988,34 +4993,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396199</v>
+        <v>396147</v>
       </c>
       <c r="R42" t="n">
-        <v>6846035</v>
+        <v>6845918</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5074,10 +5084,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123403156</v>
+        <v>123402056</v>
       </c>
       <c r="B43" t="n">
-        <v>78507</v>
+        <v>77699</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5090,37 +5100,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396197</v>
+        <v>396287</v>
       </c>
       <c r="R43" t="n">
-        <v>6845889</v>
+        <v>6845734</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5147,19 +5157,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,22 +5174,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123403854</v>
+        <v>123404225</v>
       </c>
       <c r="B44" t="n">
-        <v>77699</v>
+        <v>78507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5202,34 +5202,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396129</v>
+        <v>396199</v>
       </c>
       <c r="R44" t="n">
-        <v>6846036</v>
+        <v>6846035</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5276,22 +5276,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123407461</v>
+        <v>123403156</v>
       </c>
       <c r="B45" t="n">
-        <v>79389</v>
+        <v>78507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,37 +5304,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>396084</v>
+        <v>396197</v>
       </c>
       <c r="R45" t="n">
-        <v>6845730</v>
+        <v>6845889</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5361,9 +5361,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5378,22 +5388,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123407519</v>
+        <v>123403854</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>77699</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5406,42 +5416,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396082</v>
+        <v>396129</v>
       </c>
       <c r="R46" t="n">
-        <v>6845745</v>
+        <v>6846036</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5497,10 +5502,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123406774</v>
+        <v>123407461</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>79389</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5513,39 +5518,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396147</v>
+        <v>396084</v>
       </c>
       <c r="R47" t="n">
-        <v>6845918</v>
+        <v>6845730</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5592,12 +5592,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123407642</v>
+        <v>123402952</v>
       </c>
       <c r="B79" t="n">
-        <v>78508</v>
+        <v>78416</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8916,37 +8916,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396220</v>
+        <v>396193</v>
       </c>
       <c r="R79" t="n">
-        <v>6845759</v>
+        <v>6845821</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8973,9 +8973,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8990,22 +9000,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123402952</v>
+        <v>123408121</v>
       </c>
       <c r="B80" t="n">
-        <v>78416</v>
+        <v>78507</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9018,21 +9028,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9042,10 +9052,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>396193</v>
+        <v>396217</v>
       </c>
       <c r="R80" t="n">
-        <v>6845821</v>
+        <v>6845779</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9077,7 +9087,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9087,7 +9097,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9114,10 +9124,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123408121</v>
+        <v>123407642</v>
       </c>
       <c r="B81" t="n">
-        <v>78507</v>
+        <v>78508</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9130,37 +9140,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>396217</v>
+        <v>396220</v>
       </c>
       <c r="R81" t="n">
-        <v>6845779</v>
+        <v>6845759</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9187,19 +9197,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9214,12 +9214,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123408313</v>
+        <v>123408311</v>
       </c>
       <c r="B88" t="n">
-        <v>78155</v>
+        <v>57481</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9854,31 +9854,36 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>396446</v>
+        <v>396431</v>
       </c>
       <c r="R88" t="n">
         <v>6845432</v>
@@ -9928,22 +9933,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123408311</v>
+        <v>123408313</v>
       </c>
       <c r="B89" t="n">
-        <v>57481</v>
+        <v>78155</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9956,36 +9961,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>396431</v>
+        <v>396446</v>
       </c>
       <c r="R89" t="n">
         <v>6845432</v>
@@ -10035,12 +10035,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11942,10 +11942,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123376404</v>
+        <v>123377228</v>
       </c>
       <c r="B107" t="n">
-        <v>79389</v>
+        <v>56691</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11954,41 +11954,46 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>396632</v>
+        <v>396667</v>
       </c>
       <c r="R107" t="n">
-        <v>6845176</v>
+        <v>6845140</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12017,7 +12022,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12027,7 +12032,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12054,10 +12059,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123377228</v>
+        <v>123376404</v>
       </c>
       <c r="B108" t="n">
-        <v>56691</v>
+        <v>79389</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12066,46 +12071,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>396667</v>
+        <v>396632</v>
       </c>
       <c r="R108" t="n">
-        <v>6845140</v>
+        <v>6845176</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14388,10 +14388,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>123385567</v>
+        <v>123386532</v>
       </c>
       <c r="B129" t="n">
-        <v>79360</v>
+        <v>56691</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14400,41 +14400,46 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>396806</v>
+        <v>396722</v>
       </c>
       <c r="R129" t="n">
-        <v>6845386</v>
+        <v>6845165</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14461,9 +14466,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14478,12 +14493,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14704,10 +14719,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>123386532</v>
+        <v>123385567</v>
       </c>
       <c r="B132" t="n">
-        <v>56691</v>
+        <v>79360</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14716,46 +14731,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>396722</v>
+        <v>396806</v>
       </c>
       <c r="R132" t="n">
-        <v>6845165</v>
+        <v>6845386</v>
       </c>
       <c r="S132" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14782,19 +14792,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>18:01</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14809,12 +14809,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -15600,10 +15600,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>123379157</v>
+        <v>123385408</v>
       </c>
       <c r="B140" t="n">
-        <v>78416</v>
+        <v>79360</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15616,34 +15616,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>396733</v>
+        <v>396885</v>
       </c>
       <c r="R140" t="n">
-        <v>6845033</v>
+        <v>6845332</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15712,10 +15712,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>123385506</v>
+        <v>123379787</v>
       </c>
       <c r="B141" t="n">
-        <v>79389</v>
+        <v>78508</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15728,37 +15728,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>396817</v>
+        <v>396858</v>
       </c>
       <c r="R141" t="n">
-        <v>6845368</v>
+        <v>6845010</v>
       </c>
       <c r="S141" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15785,19 +15785,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15812,22 +15802,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Lars-Erik Nilsson, Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>123377962</v>
+        <v>123381657</v>
       </c>
       <c r="B142" t="n">
-        <v>79881</v>
+        <v>79360</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15836,40 +15826,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>396727</v>
+        <v>396972</v>
       </c>
       <c r="R142" t="n">
-        <v>6845110</v>
+        <v>6845189</v>
       </c>
       <c r="S142" t="n">
         <v>4</v>
@@ -15901,7 +15889,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15911,7 +15899,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15920,7 +15908,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15932,17 +15919,17 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>123379369</v>
+        <v>123379157</v>
       </c>
       <c r="B143" t="n">
-        <v>78771</v>
+        <v>78416</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15955,37 +15942,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>396782</v>
+        <v>396733</v>
       </c>
       <c r="R143" t="n">
-        <v>6845074</v>
+        <v>6845033</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16014,7 +16001,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16024,7 +16011,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16039,22 +16026,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>123385408</v>
+        <v>123385506</v>
       </c>
       <c r="B144" t="n">
-        <v>79360</v>
+        <v>79389</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16067,21 +16054,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16091,10 +16078,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>396885</v>
+        <v>396817</v>
       </c>
       <c r="R144" t="n">
-        <v>6845332</v>
+        <v>6845368</v>
       </c>
       <c r="S144" t="n">
         <v>4</v>
@@ -16126,7 +16113,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16136,7 +16123,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16156,17 +16143,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander, Lars-Erik Nilsson, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>123379787</v>
+        <v>123377962</v>
       </c>
       <c r="B145" t="n">
-        <v>78508</v>
+        <v>79881</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16175,41 +16162,43 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>396858</v>
+        <v>396727</v>
       </c>
       <c r="R145" t="n">
-        <v>6845010</v>
+        <v>6845110</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16236,39 +16225,50 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123381657</v>
+        <v>123379369</v>
       </c>
       <c r="B146" t="n">
-        <v>79360</v>
+        <v>78771</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16281,37 +16281,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>396972</v>
+        <v>396782</v>
       </c>
       <c r="R146" t="n">
-        <v>6845189</v>
+        <v>6845074</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16365,12 +16365,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -17141,10 +17141,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>123378915</v>
+        <v>123381093</v>
       </c>
       <c r="B154" t="n">
-        <v>78416</v>
+        <v>78508</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17157,37 +17157,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>396782</v>
+        <v>396919</v>
       </c>
       <c r="R154" t="n">
-        <v>6845074</v>
+        <v>6845236</v>
       </c>
       <c r="S154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17241,22 +17241,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>123381093</v>
+        <v>123378915</v>
       </c>
       <c r="B155" t="n">
-        <v>78508</v>
+        <v>78416</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17269,37 +17269,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>396919</v>
+        <v>396782</v>
       </c>
       <c r="R155" t="n">
-        <v>6845236</v>
+        <v>6845074</v>
       </c>
       <c r="S155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17353,12 +17353,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -18791,10 +18791,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>123381981</v>
+        <v>123380397</v>
       </c>
       <c r="B169" t="n">
-        <v>79389</v>
+        <v>78416</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18807,34 +18807,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>396988</v>
+        <v>396797</v>
       </c>
       <c r="R169" t="n">
-        <v>6845143</v>
+        <v>6845120</v>
       </c>
       <c r="S169" t="n">
         <v>4</v>
@@ -18866,7 +18871,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18876,7 +18881,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18903,10 +18908,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>123383301</v>
+        <v>123381981</v>
       </c>
       <c r="B170" t="n">
-        <v>92238</v>
+        <v>79389</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18915,47 +18920,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>397041</v>
+        <v>396988</v>
       </c>
       <c r="R170" t="n">
-        <v>6845139</v>
+        <v>6845143</v>
       </c>
       <c r="S170" t="n">
         <v>4</v>
@@ -18987,7 +18983,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18997,7 +18993,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19024,10 +19020,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>123380397</v>
+        <v>123383301</v>
       </c>
       <c r="B171" t="n">
-        <v>78416</v>
+        <v>92238</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19036,43 +19032,47 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>396797</v>
+        <v>397041</v>
       </c>
       <c r="R171" t="n">
-        <v>6845120</v>
+        <v>6845139</v>
       </c>
       <c r="S171" t="n">
         <v>4</v>
@@ -19104,7 +19104,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD171" t="b">

--- a/artfynd/A 6679-2025 artfynd.xlsx
+++ b/artfynd/A 6679-2025 artfynd.xlsx
@@ -11941,10 +11941,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123376759</v>
+        <v>123376924</v>
       </c>
       <c r="B107" t="n">
-        <v>79393</v>
+        <v>78420</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11957,30 +11957,25 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11988,10 +11983,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>396660</v>
+        <v>396665</v>
       </c>
       <c r="R107" t="n">
-        <v>6845132</v>
+        <v>6845134</v>
       </c>
       <c r="S107" t="n">
         <v>4</v>
@@ -12023,7 +12018,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12033,7 +12028,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12061,10 +12056,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123376924</v>
+        <v>123376759</v>
       </c>
       <c r="B108" t="n">
-        <v>78420</v>
+        <v>79393</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12077,25 +12072,30 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>396665</v>
+        <v>396660</v>
       </c>
       <c r="R108" t="n">
-        <v>6845134</v>
+        <v>6845132</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12176,10 +12176,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123377546</v>
+        <v>123376553</v>
       </c>
       <c r="B109" t="n">
-        <v>77703</v>
+        <v>78870</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12192,34 +12192,43 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>396689</v>
+        <v>396650</v>
       </c>
       <c r="R109" t="n">
-        <v>6845116</v>
+        <v>6845130</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12278,10 +12287,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123376553</v>
+        <v>123377557</v>
       </c>
       <c r="B110" t="n">
-        <v>78870</v>
+        <v>79364</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12294,46 +12303,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>396650</v>
+        <v>396667</v>
       </c>
       <c r="R110" t="n">
-        <v>6845130</v>
+        <v>6845140</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12360,9 +12360,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12377,22 +12387,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123377557</v>
+        <v>123377546</v>
       </c>
       <c r="B111" t="n">
-        <v>79364</v>
+        <v>77703</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12405,21 +12415,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12429,13 +12439,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>396667</v>
+        <v>396689</v>
       </c>
       <c r="R111" t="n">
-        <v>6845140</v>
+        <v>6845116</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12462,19 +12472,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12489,12 +12489,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13614,10 +13614,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123401886</v>
+        <v>123408728</v>
       </c>
       <c r="B122" t="n">
-        <v>79393</v>
+        <v>57851</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13626,41 +13626,46 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>396474</v>
+        <v>396542</v>
       </c>
       <c r="R122" t="n">
-        <v>6845113</v>
+        <v>6845325</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13687,19 +13692,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13714,22 +13709,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123408728</v>
+        <v>123401886</v>
       </c>
       <c r="B123" t="n">
-        <v>57851</v>
+        <v>79393</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13738,46 +13733,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>396542</v>
+        <v>396474</v>
       </c>
       <c r="R123" t="n">
-        <v>6845325</v>
+        <v>6845113</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13804,9 +13794,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13821,12 +13821,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -16618,7 +16618,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>123384283</v>
+        <v>123384371</v>
       </c>
       <c r="B149" t="n">
         <v>79393</v>
@@ -16658,10 +16658,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>396987</v>
+        <v>396967</v>
       </c>
       <c r="R149" t="n">
-        <v>6845180</v>
+        <v>6845183</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -16693,7 +16693,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16730,7 +16730,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>123384371</v>
+        <v>123384283</v>
       </c>
       <c r="B150" t="n">
         <v>79393</v>
@@ -16770,10 +16770,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>396967</v>
+        <v>396987</v>
       </c>
       <c r="R150" t="n">
-        <v>6845183</v>
+        <v>6845180</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17824,10 +17824,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>123386516</v>
+        <v>123385003</v>
       </c>
       <c r="B160" t="n">
-        <v>79393</v>
+        <v>78420</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17840,34 +17840,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>396719</v>
+        <v>396940</v>
       </c>
       <c r="R160" t="n">
-        <v>6845165</v>
+        <v>6845309</v>
       </c>
       <c r="S160" t="n">
         <v>4</v>
@@ -17899,7 +17904,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17909,7 +17914,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17936,10 +17941,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>123385003</v>
+        <v>123386516</v>
       </c>
       <c r="B161" t="n">
-        <v>78420</v>
+        <v>79393</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17952,39 +17957,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>396940</v>
+        <v>396719</v>
       </c>
       <c r="R161" t="n">
-        <v>6845309</v>
+        <v>6845165</v>
       </c>
       <c r="S161" t="n">
         <v>4</v>
@@ -18016,7 +18016,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19049,10 +19049,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>123385567</v>
+        <v>123385540</v>
       </c>
       <c r="B171" t="n">
-        <v>79364</v>
+        <v>79393</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19065,37 +19065,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>396806</v>
+        <v>396819</v>
       </c>
       <c r="R171" t="n">
-        <v>6845386</v>
+        <v>6845391</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19122,9 +19122,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19139,22 +19149,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>123385540</v>
+        <v>123385567</v>
       </c>
       <c r="B172" t="n">
-        <v>79393</v>
+        <v>79364</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19167,37 +19177,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>396819</v>
+        <v>396806</v>
       </c>
       <c r="R172" t="n">
-        <v>6845391</v>
+        <v>6845386</v>
       </c>
       <c r="S172" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19224,19 +19234,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19251,12 +19251,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>

--- a/artfynd/A 6679-2025 artfynd.xlsx
+++ b/artfynd/A 6679-2025 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408217</v>
+        <v>123403202</v>
       </c>
       <c r="B6" t="n">
-        <v>78426</v>
+        <v>79399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396217</v>
+        <v>396202</v>
       </c>
       <c r="R6" t="n">
-        <v>6845738</v>
+        <v>6845898</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123403202</v>
+        <v>123408217</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>78426</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396202</v>
+        <v>396217</v>
       </c>
       <c r="R7" t="n">
-        <v>6845898</v>
+        <v>6845738</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123407113</v>
+        <v>123402069</v>
       </c>
       <c r="B8" t="n">
-        <v>78518</v>
+        <v>80734</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,37 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396115</v>
+        <v>396287</v>
       </c>
       <c r="R8" t="n">
-        <v>6845968</v>
+        <v>6845734</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,19 +1390,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,19 +1407,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123407471</v>
+        <v>123407113</v>
       </c>
       <c r="B9" t="n">
         <v>78518</v>
@@ -1469,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396183</v>
+        <v>396115</v>
       </c>
       <c r="R9" t="n">
-        <v>6845919</v>
+        <v>6845968</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123402042</v>
+        <v>123407471</v>
       </c>
       <c r="B10" t="n">
-        <v>79370</v>
+        <v>78518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,37 +1547,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>396287</v>
+        <v>396183</v>
       </c>
       <c r="R10" t="n">
-        <v>6845734</v>
+        <v>6845919</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,9 +1604,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,22 +1631,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123402069</v>
+        <v>123402042</v>
       </c>
       <c r="B11" t="n">
-        <v>80734</v>
+        <v>79370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123402307</v>
+        <v>123404624</v>
       </c>
       <c r="B24" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3054,39 +3054,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>396302</v>
+        <v>396107</v>
       </c>
       <c r="R24" t="n">
-        <v>6845760</v>
+        <v>6845974</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,10 +3140,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123404624</v>
+        <v>123402307</v>
       </c>
       <c r="B25" t="n">
-        <v>78518</v>
+        <v>57487</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,34 +3156,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>396107</v>
+        <v>396302</v>
       </c>
       <c r="R25" t="n">
-        <v>6845974</v>
+        <v>6845760</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123402432</v>
+        <v>123401136</v>
       </c>
       <c r="B30" t="n">
-        <v>80734</v>
+        <v>78426</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,37 +3681,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>396300</v>
+        <v>396244</v>
       </c>
       <c r="R30" t="n">
-        <v>6845775</v>
+        <v>6845640</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3738,19 +3738,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,22 +3755,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123401136</v>
+        <v>123402432</v>
       </c>
       <c r="B31" t="n">
-        <v>78426</v>
+        <v>80734</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3793,37 +3783,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>396244</v>
+        <v>396300</v>
       </c>
       <c r="R31" t="n">
-        <v>6845640</v>
+        <v>6845775</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3850,9 +3840,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,12 +3867,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123401802</v>
+        <v>123408154</v>
       </c>
       <c r="B52" t="n">
-        <v>57503</v>
+        <v>78517</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6000,42 +6000,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>396262</v>
+        <v>396218</v>
       </c>
       <c r="R52" t="n">
-        <v>6845711</v>
+        <v>6845772</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6062,9 +6057,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6079,22 +6084,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123408154</v>
+        <v>123403759</v>
       </c>
       <c r="B53" t="n">
-        <v>78517</v>
+        <v>79370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6107,37 +6112,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>396218</v>
+        <v>396263</v>
       </c>
       <c r="R53" t="n">
-        <v>6845772</v>
+        <v>6845967</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6164,19 +6169,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6191,22 +6186,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123403759</v>
+        <v>123401802</v>
       </c>
       <c r="B54" t="n">
-        <v>79370</v>
+        <v>57503</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6219,34 +6214,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>396263</v>
+        <v>396262</v>
       </c>
       <c r="R54" t="n">
-        <v>6845967</v>
+        <v>6845711</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7253,10 +7253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123403633</v>
+        <v>123406836</v>
       </c>
       <c r="B64" t="n">
-        <v>78876</v>
+        <v>78426</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7269,51 +7269,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>967</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>396198</v>
+        <v>396176</v>
       </c>
       <c r="R64" t="n">
-        <v>6845932</v>
+        <v>6845908</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7340,19 +7326,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7367,22 +7343,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123406836</v>
+        <v>123402056</v>
       </c>
       <c r="B65" t="n">
-        <v>78426</v>
+        <v>77709</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7395,34 +7371,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>396176</v>
+        <v>396287</v>
       </c>
       <c r="R65" t="n">
-        <v>6845908</v>
+        <v>6845734</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7481,10 +7457,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123402056</v>
+        <v>123407461</v>
       </c>
       <c r="B66" t="n">
-        <v>77709</v>
+        <v>79399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7497,34 +7473,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>396287</v>
+        <v>396084</v>
       </c>
       <c r="R66" t="n">
-        <v>6845734</v>
+        <v>6845730</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7583,10 +7559,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123407461</v>
+        <v>123407465</v>
       </c>
       <c r="B67" t="n">
-        <v>79399</v>
+        <v>78517</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7599,34 +7575,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>396084</v>
+        <v>396196</v>
       </c>
       <c r="R67" t="n">
-        <v>6845730</v>
+        <v>6845788</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7673,22 +7649,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123407465</v>
+        <v>123407557</v>
       </c>
       <c r="B68" t="n">
-        <v>78517</v>
+        <v>57487</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7701,37 +7677,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>396196</v>
+        <v>396092</v>
       </c>
       <c r="R68" t="n">
-        <v>6845788</v>
+        <v>6845720</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7775,22 +7756,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123407557</v>
+        <v>123403974</v>
       </c>
       <c r="B69" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7803,42 +7784,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>396092</v>
+        <v>396139</v>
       </c>
       <c r="R69" t="n">
-        <v>6845720</v>
+        <v>6846046</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7894,10 +7870,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123403974</v>
+        <v>123403633</v>
       </c>
       <c r="B70" t="n">
-        <v>78518</v>
+        <v>78876</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7910,37 +7886,51 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>396139</v>
+        <v>396198</v>
       </c>
       <c r="R70" t="n">
-        <v>6846046</v>
+        <v>6845932</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7967,9 +7957,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7984,22 +7984,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123402235</v>
+        <v>123403126</v>
       </c>
       <c r="B71" t="n">
-        <v>57487</v>
+        <v>79399</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8012,42 +8012,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>396281</v>
+        <v>396200</v>
       </c>
       <c r="R71" t="n">
-        <v>6845766</v>
+        <v>6845919</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8074,19 +8069,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8101,22 +8086,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123403126</v>
+        <v>123403765</v>
       </c>
       <c r="B72" t="n">
-        <v>79399</v>
+        <v>79891</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8125,41 +8110,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>396200</v>
+        <v>396203</v>
       </c>
       <c r="R72" t="n">
-        <v>6845919</v>
+        <v>6845971</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8186,9 +8171,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8203,22 +8198,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123403765</v>
+        <v>123402235</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>57487</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8227,38 +8222,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>396203</v>
+        <v>396281</v>
       </c>
       <c r="R73" t="n">
-        <v>6845971</v>
+        <v>6845766</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8866,10 +8866,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123406999</v>
+        <v>123403734</v>
       </c>
       <c r="B79" t="n">
-        <v>78518</v>
+        <v>79399</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8882,21 +8882,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8906,10 +8906,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396169</v>
+        <v>396152</v>
       </c>
       <c r="R79" t="n">
-        <v>6845810</v>
+        <v>6845999</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8968,10 +8968,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123403734</v>
+        <v>123406999</v>
       </c>
       <c r="B80" t="n">
-        <v>79399</v>
+        <v>78518</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8984,21 +8984,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>396152</v>
+        <v>396169</v>
       </c>
       <c r="R80" t="n">
-        <v>6845999</v>
+        <v>6845810</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -13176,10 +13176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123399598</v>
+        <v>123401886</v>
       </c>
       <c r="B118" t="n">
-        <v>78517</v>
+        <v>79399</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13192,21 +13192,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13216,10 +13216,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>396640</v>
+        <v>396474</v>
       </c>
       <c r="R118" t="n">
-        <v>6845024</v>
+        <v>6845113</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13288,10 +13288,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123399779</v>
+        <v>123399598</v>
       </c>
       <c r="B119" t="n">
-        <v>57487</v>
+        <v>78517</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13304,42 +13304,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>396519</v>
+        <v>396640</v>
       </c>
       <c r="R119" t="n">
-        <v>6845294</v>
+        <v>6845024</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13366,9 +13361,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13383,22 +13388,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123401886</v>
+        <v>123399779</v>
       </c>
       <c r="B120" t="n">
-        <v>79399</v>
+        <v>57487</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13411,37 +13416,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>396474</v>
+        <v>396519</v>
       </c>
       <c r="R120" t="n">
-        <v>6845113</v>
+        <v>6845294</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13468,19 +13478,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13495,12 +13495,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14388,10 +14388,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>123379451</v>
+        <v>123385567</v>
       </c>
       <c r="B129" t="n">
-        <v>79399</v>
+        <v>79370</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14404,37 +14404,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>396819</v>
+        <v>396806</v>
       </c>
       <c r="R129" t="n">
-        <v>6844919</v>
+        <v>6845386</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14461,19 +14461,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14488,19 +14478,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>123377850</v>
+        <v>123379451</v>
       </c>
       <c r="B130" t="n">
         <v>79399</v>
@@ -14534,23 +14524,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>396726</v>
+        <v>396819</v>
       </c>
       <c r="R130" t="n">
-        <v>6845127</v>
+        <v>6844919</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
@@ -14582,7 +14565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14592,7 +14575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14601,7 +14584,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14613,17 +14595,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>123385567</v>
+        <v>123377850</v>
       </c>
       <c r="B131" t="n">
-        <v>79370</v>
+        <v>79399</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14636,37 +14618,44 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>396806</v>
+        <v>396726</v>
       </c>
       <c r="R131" t="n">
-        <v>6845386</v>
+        <v>6845127</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14693,29 +14682,40 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -15389,10 +15389,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>123385250</v>
+        <v>123378915</v>
       </c>
       <c r="B138" t="n">
-        <v>79399</v>
+        <v>78426</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15405,21 +15405,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15429,13 +15429,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>396864</v>
+        <v>396782</v>
       </c>
       <c r="R138" t="n">
-        <v>6845294</v>
+        <v>6845074</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15462,9 +15462,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15479,22 +15489,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>123378915</v>
+        <v>123385250</v>
       </c>
       <c r="B139" t="n">
-        <v>78426</v>
+        <v>79399</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15507,21 +15517,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15531,13 +15541,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>396782</v>
+        <v>396864</v>
       </c>
       <c r="R139" t="n">
-        <v>6845074</v>
+        <v>6845294</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15564,19 +15574,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15591,12 +15591,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16375,10 +16375,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>123386532</v>
+        <v>123381981</v>
       </c>
       <c r="B147" t="n">
-        <v>56697</v>
+        <v>79399</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16387,43 +16387,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>396722</v>
+        <v>396988</v>
       </c>
       <c r="R147" t="n">
-        <v>6845165</v>
+        <v>6845143</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -16455,7 +16450,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16465,7 +16460,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16492,10 +16487,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>123381981</v>
+        <v>123384388</v>
       </c>
       <c r="B148" t="n">
-        <v>79399</v>
+        <v>78517</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16508,34 +16503,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>396988</v>
+        <v>396967</v>
       </c>
       <c r="R148" t="n">
-        <v>6845143</v>
+        <v>6845183</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16567,7 +16562,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16577,7 +16572,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16604,10 +16599,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>123384388</v>
+        <v>123379008</v>
       </c>
       <c r="B149" t="n">
-        <v>78517</v>
+        <v>79399</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16620,34 +16615,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>396967</v>
+        <v>396729</v>
       </c>
       <c r="R149" t="n">
-        <v>6845183</v>
+        <v>6845058</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -16679,7 +16674,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16689,7 +16684,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16716,10 +16711,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>123379008</v>
+        <v>123386532</v>
       </c>
       <c r="B150" t="n">
-        <v>79399</v>
+        <v>56697</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16728,38 +16723,43 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>396729</v>
+        <v>396722</v>
       </c>
       <c r="R150" t="n">
-        <v>6845058</v>
+        <v>6845165</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16791,7 +16791,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17393,10 +17393,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>123384079</v>
+        <v>123380073</v>
       </c>
       <c r="B156" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17409,37 +17409,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>396977</v>
+        <v>396805</v>
       </c>
       <c r="R156" t="n">
-        <v>6845168</v>
+        <v>6845099</v>
       </c>
       <c r="S156" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17466,19 +17471,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>16:34</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17493,22 +17488,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>123380073</v>
+        <v>123385270</v>
       </c>
       <c r="B157" t="n">
-        <v>57503</v>
+        <v>78517</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17521,39 +17516,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>396805</v>
+        <v>396864</v>
       </c>
       <c r="R157" t="n">
-        <v>6845099</v>
+        <v>6845294</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17612,10 +17602,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>123385270</v>
+        <v>123384079</v>
       </c>
       <c r="B158" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17628,37 +17618,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>396864</v>
+        <v>396977</v>
       </c>
       <c r="R158" t="n">
-        <v>6845294</v>
+        <v>6845168</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17685,9 +17675,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17702,22 +17702,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>123380545</v>
+        <v>123380521</v>
       </c>
       <c r="B159" t="n">
-        <v>79370</v>
+        <v>57503</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17730,37 +17730,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>396850</v>
+        <v>396848</v>
       </c>
       <c r="R159" t="n">
-        <v>6845163</v>
+        <v>6845171</v>
       </c>
       <c r="S159" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17787,19 +17792,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17814,22 +17809,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>123380521</v>
+        <v>123380545</v>
       </c>
       <c r="B160" t="n">
-        <v>57503</v>
+        <v>79370</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17842,42 +17837,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>396848</v>
+        <v>396850</v>
       </c>
       <c r="R160" t="n">
-        <v>6845171</v>
+        <v>6845163</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17904,9 +17894,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17921,12 +17921,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>123386610</v>
+        <v>123385225</v>
       </c>
       <c r="B167" t="n">
-        <v>78426</v>
+        <v>78518</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18626,37 +18626,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>396715</v>
+        <v>396864</v>
       </c>
       <c r="R167" t="n">
-        <v>6845143</v>
+        <v>6845294</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18683,19 +18683,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18710,22 +18700,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>123384781</v>
+        <v>123377962</v>
       </c>
       <c r="B168" t="n">
-        <v>78876</v>
+        <v>79891</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18734,41 +18724,43 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>967</v>
+        <v>6462</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>396953</v>
+        <v>396727</v>
       </c>
       <c r="R168" t="n">
-        <v>6845254</v>
+        <v>6845110</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18795,39 +18787,50 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>123377962</v>
+        <v>123382029</v>
       </c>
       <c r="B169" t="n">
-        <v>79891</v>
+        <v>79399</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18836,43 +18839,41 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>396727</v>
+        <v>397016</v>
       </c>
       <c r="R169" t="n">
-        <v>6845110</v>
+        <v>6845132</v>
       </c>
       <c r="S169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18901,7 +18902,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18911,7 +18912,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18920,29 +18921,28 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>123382029</v>
+        <v>123384240</v>
       </c>
       <c r="B170" t="n">
-        <v>79399</v>
+        <v>78517</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18955,37 +18955,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>397016</v>
+        <v>396984</v>
       </c>
       <c r="R170" t="n">
-        <v>6845132</v>
+        <v>6845181</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19012,19 +19012,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19039,22 +19029,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>123384240</v>
+        <v>123386610</v>
       </c>
       <c r="B171" t="n">
-        <v>78517</v>
+        <v>78426</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19067,37 +19057,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>396984</v>
+        <v>396715</v>
       </c>
       <c r="R171" t="n">
-        <v>6845181</v>
+        <v>6845143</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19124,9 +19114,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19141,22 +19141,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>123385225</v>
+        <v>123384781</v>
       </c>
       <c r="B172" t="n">
-        <v>78518</v>
+        <v>78876</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19169,34 +19169,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>396864</v>
+        <v>396953</v>
       </c>
       <c r="R172" t="n">
-        <v>6845294</v>
+        <v>6845254</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>

--- a/artfynd/A 6679-2025 artfynd.xlsx
+++ b/artfynd/A 6679-2025 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123401667</v>
+        <v>123402545</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>57640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,34 +1761,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>396252</v>
+        <v>396287</v>
       </c>
       <c r="R12" t="n">
-        <v>6845715</v>
+        <v>6845788</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1820,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123407519</v>
+        <v>123401667</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>79399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,42 +1882,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>396082</v>
+        <v>396252</v>
       </c>
       <c r="R13" t="n">
-        <v>6845745</v>
+        <v>6845715</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,9 +1939,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,22 +1966,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123403761</v>
+        <v>123407949</v>
       </c>
       <c r="B14" t="n">
-        <v>78518</v>
+        <v>78517</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,37 +1994,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>396152</v>
+        <v>396193</v>
       </c>
       <c r="R14" t="n">
-        <v>6845999</v>
+        <v>6845802</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,9 +2051,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,22 +2078,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123407642</v>
+        <v>123407801</v>
       </c>
       <c r="B15" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>396220</v>
+        <v>396228</v>
       </c>
       <c r="R15" t="n">
-        <v>6845759</v>
+        <v>6845716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123407949</v>
+        <v>123407519</v>
       </c>
       <c r="B16" t="n">
-        <v>78517</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,37 +2208,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396193</v>
+        <v>396082</v>
       </c>
       <c r="R16" t="n">
-        <v>6845802</v>
+        <v>6845745</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,19 +2270,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,22 +2287,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123407801</v>
+        <v>123405032</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,34 +2315,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>396228</v>
+        <v>396107</v>
       </c>
       <c r="R17" t="n">
-        <v>6845716</v>
+        <v>6845974</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,22 +2394,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123406592</v>
+        <v>123403761</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,39 +2422,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396156</v>
+        <v>396152</v>
       </c>
       <c r="R18" t="n">
-        <v>6845922</v>
+        <v>6845999</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,11 +2484,6 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack ovan bohål.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2482,22 +2496,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123405032</v>
+        <v>123407642</v>
       </c>
       <c r="B19" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,39 +2524,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396107</v>
+        <v>396220</v>
       </c>
       <c r="R19" t="n">
-        <v>6845974</v>
+        <v>6845759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,22 +2598,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123402545</v>
+        <v>123407967</v>
       </c>
       <c r="B20" t="n">
-        <v>57640</v>
+        <v>79399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,46 +2626,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>396287</v>
+        <v>396252</v>
       </c>
       <c r="R20" t="n">
-        <v>6845788</v>
+        <v>6845578</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2683,19 +2683,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,22 +2700,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123407967</v>
+        <v>123402921</v>
       </c>
       <c r="B21" t="n">
-        <v>79399</v>
+        <v>77709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,21 +2728,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>396252</v>
+        <v>396195</v>
       </c>
       <c r="R21" t="n">
-        <v>6845578</v>
+        <v>6845838</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,10 +2814,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123402921</v>
+        <v>123408121</v>
       </c>
       <c r="B22" t="n">
-        <v>77709</v>
+        <v>78517</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,37 +2830,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>396195</v>
+        <v>396217</v>
       </c>
       <c r="R22" t="n">
-        <v>6845838</v>
+        <v>6845779</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,9 +2887,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2914,22 +2914,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123408121</v>
+        <v>123402307</v>
       </c>
       <c r="B23" t="n">
-        <v>78517</v>
+        <v>57487</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,37 +2942,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>396217</v>
+        <v>396302</v>
       </c>
       <c r="R23" t="n">
-        <v>6845779</v>
+        <v>6845760</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2999,19 +3004,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,12 +3021,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3140,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123402307</v>
+        <v>123407661</v>
       </c>
       <c r="B25" t="n">
-        <v>57487</v>
+        <v>79399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3156,39 +3151,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>396302</v>
+        <v>396150</v>
       </c>
       <c r="R25" t="n">
-        <v>6845760</v>
+        <v>6845673</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123407661</v>
+        <v>123402929</v>
       </c>
       <c r="B26" t="n">
-        <v>79399</v>
+        <v>57503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,34 +3253,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>396150</v>
+        <v>396208</v>
       </c>
       <c r="R26" t="n">
-        <v>6845673</v>
+        <v>6845869</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,22 +3332,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123402929</v>
+        <v>123407372</v>
       </c>
       <c r="B27" t="n">
-        <v>57503</v>
+        <v>57487</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,16 +3360,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3385,7 +3380,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3394,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>396208</v>
+        <v>396167</v>
       </c>
       <c r="R27" t="n">
-        <v>6845869</v>
+        <v>6845767</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123407372</v>
+        <v>123402477</v>
       </c>
       <c r="B28" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,39 +3467,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>396167</v>
+        <v>396272</v>
       </c>
       <c r="R28" t="n">
-        <v>6845767</v>
+        <v>6845833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,22 +3541,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123402477</v>
+        <v>123401136</v>
       </c>
       <c r="B29" t="n">
-        <v>78518</v>
+        <v>78426</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,21 +3569,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>396272</v>
+        <v>396244</v>
       </c>
       <c r="R29" t="n">
-        <v>6845833</v>
+        <v>6845640</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3665,10 +3655,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123401136</v>
+        <v>123402432</v>
       </c>
       <c r="B30" t="n">
-        <v>78426</v>
+        <v>80734</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,37 +3671,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>396244</v>
+        <v>396300</v>
       </c>
       <c r="R30" t="n">
-        <v>6845640</v>
+        <v>6845775</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3738,9 +3728,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3755,22 +3755,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123402432</v>
+        <v>123403119</v>
       </c>
       <c r="B31" t="n">
-        <v>80734</v>
+        <v>78165</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,37 +3783,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>396300</v>
+        <v>396195</v>
       </c>
       <c r="R31" t="n">
-        <v>6845775</v>
+        <v>6845838</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3840,19 +3840,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,22 +3857,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123403119</v>
+        <v>123403054</v>
       </c>
       <c r="B32" t="n">
-        <v>78165</v>
+        <v>78426</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,37 +3885,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396195</v>
+        <v>396190</v>
       </c>
       <c r="R32" t="n">
-        <v>6845838</v>
+        <v>6845863</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3952,9 +3942,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,19 +3969,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123403054</v>
+        <v>123403123</v>
       </c>
       <c r="B33" t="n">
         <v>78426</v>
@@ -4017,17 +4017,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>396190</v>
+        <v>396200</v>
       </c>
       <c r="R33" t="n">
-        <v>6845863</v>
+        <v>6845919</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4054,19 +4054,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,19 +4071,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123403123</v>
+        <v>123404309</v>
       </c>
       <c r="B34" t="n">
         <v>78426</v>
@@ -4133,10 +4123,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396200</v>
+        <v>396057</v>
       </c>
       <c r="R34" t="n">
-        <v>6845919</v>
+        <v>6846006</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4195,10 +4185,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123404309</v>
+        <v>123402005</v>
       </c>
       <c r="B35" t="n">
-        <v>78426</v>
+        <v>74870</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4211,34 +4201,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396057</v>
+        <v>396287</v>
       </c>
       <c r="R35" t="n">
-        <v>6846006</v>
+        <v>6845734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,17 +4280,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123402005</v>
+        <v>123407585</v>
       </c>
       <c r="B36" t="n">
-        <v>74870</v>
+        <v>79399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4313,37 +4303,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>310</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>396287</v>
+        <v>396154</v>
       </c>
       <c r="R36" t="n">
-        <v>6845734</v>
+        <v>6845888</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4370,9 +4360,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4387,19 +4387,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Malte Lindberg</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123407585</v>
+        <v>123402278</v>
       </c>
       <c r="B37" t="n">
         <v>79399</v>
@@ -4435,17 +4435,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>396154</v>
+        <v>396302</v>
       </c>
       <c r="R37" t="n">
-        <v>6845888</v>
+        <v>6845760</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4472,19 +4472,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4499,19 +4489,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123402278</v>
+        <v>123407763</v>
       </c>
       <c r="B38" t="n">
         <v>79399</v>
@@ -4547,14 +4537,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>396302</v>
+        <v>396169</v>
       </c>
       <c r="R38" t="n">
-        <v>6845760</v>
+        <v>6845665</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4613,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123407763</v>
+        <v>123407432</v>
       </c>
       <c r="B39" t="n">
-        <v>79399</v>
+        <v>56697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4625,41 +4615,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>396169</v>
+        <v>396184</v>
       </c>
       <c r="R39" t="n">
-        <v>6845665</v>
+        <v>6845920</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4686,9 +4681,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4703,22 +4708,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123407432</v>
+        <v>123406540</v>
       </c>
       <c r="B40" t="n">
-        <v>56697</v>
+        <v>78517</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4727,46 +4732,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>396184</v>
+        <v>396138</v>
       </c>
       <c r="R40" t="n">
-        <v>6845920</v>
+        <v>6845991</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4793,19 +4793,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4820,19 +4810,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123406540</v>
+        <v>123404524</v>
       </c>
       <c r="B41" t="n">
         <v>78517</v>
@@ -4872,10 +4862,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396138</v>
+        <v>396090</v>
       </c>
       <c r="R41" t="n">
-        <v>6845991</v>
+        <v>6845976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4934,10 +4924,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123404524</v>
+        <v>123408392</v>
       </c>
       <c r="B42" t="n">
-        <v>78517</v>
+        <v>79399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4950,37 +4940,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396090</v>
+        <v>396264</v>
       </c>
       <c r="R42" t="n">
-        <v>6845976</v>
+        <v>6845661</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5007,9 +4997,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5024,22 +5024,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123403134</v>
+        <v>123403854</v>
       </c>
       <c r="B43" t="n">
-        <v>78426</v>
+        <v>77709</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5052,37 +5052,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396200</v>
+        <v>396129</v>
       </c>
       <c r="R43" t="n">
-        <v>6845887</v>
+        <v>6846036</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5109,19 +5109,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5136,22 +5126,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123403854</v>
+        <v>123403134</v>
       </c>
       <c r="B44" t="n">
-        <v>77709</v>
+        <v>78426</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5164,37 +5154,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396129</v>
+        <v>396200</v>
       </c>
       <c r="R44" t="n">
-        <v>6846036</v>
+        <v>6845887</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5221,9 +5211,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5238,22 +5238,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123408392</v>
+        <v>123403866</v>
       </c>
       <c r="B45" t="n">
-        <v>79399</v>
+        <v>78165</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5266,37 +5266,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>396264</v>
+        <v>396129</v>
       </c>
       <c r="R45" t="n">
-        <v>6845661</v>
+        <v>6846036</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5323,19 +5323,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5350,22 +5340,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123403866</v>
+        <v>123404225</v>
       </c>
       <c r="B46" t="n">
-        <v>78165</v>
+        <v>78517</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,34 +5368,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396129</v>
+        <v>396199</v>
       </c>
       <c r="R46" t="n">
-        <v>6846036</v>
+        <v>6846035</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5452,22 +5442,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123404225</v>
+        <v>123401152</v>
       </c>
       <c r="B47" t="n">
-        <v>78517</v>
+        <v>79399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5480,34 +5470,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396199</v>
+        <v>396244</v>
       </c>
       <c r="R47" t="n">
-        <v>6846035</v>
+        <v>6845640</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5554,19 +5544,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123401152</v>
+        <v>123403637</v>
       </c>
       <c r="B48" t="n">
         <v>79399</v>
@@ -5602,17 +5592,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396244</v>
+        <v>396198</v>
       </c>
       <c r="R48" t="n">
-        <v>6845640</v>
+        <v>6845932</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5639,9 +5629,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5656,22 +5656,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123403637</v>
+        <v>123404245</v>
       </c>
       <c r="B49" t="n">
-        <v>79399</v>
+        <v>78518</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5684,37 +5684,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>396198</v>
+        <v>396199</v>
       </c>
       <c r="R49" t="n">
-        <v>6845932</v>
+        <v>6846035</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5741,19 +5741,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5768,22 +5758,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123404245</v>
+        <v>123404391</v>
       </c>
       <c r="B50" t="n">
-        <v>78518</v>
+        <v>79399</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5796,34 +5786,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>396199</v>
+        <v>396076</v>
       </c>
       <c r="R50" t="n">
-        <v>6846035</v>
+        <v>6846002</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5870,22 +5860,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123404391</v>
+        <v>123408154</v>
       </c>
       <c r="B51" t="n">
-        <v>79399</v>
+        <v>78517</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5898,37 +5888,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>396076</v>
+        <v>396218</v>
       </c>
       <c r="R51" t="n">
-        <v>6846002</v>
+        <v>6845772</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5955,9 +5945,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5972,22 +5972,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123408154</v>
+        <v>123403759</v>
       </c>
       <c r="B52" t="n">
-        <v>78517</v>
+        <v>79370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6000,37 +6000,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>396218</v>
+        <v>396263</v>
       </c>
       <c r="R52" t="n">
-        <v>6845772</v>
+        <v>6845967</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6057,19 +6057,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6084,22 +6074,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123403759</v>
+        <v>123401802</v>
       </c>
       <c r="B53" t="n">
-        <v>79370</v>
+        <v>57503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6112,34 +6102,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>396263</v>
+        <v>396262</v>
       </c>
       <c r="R53" t="n">
-        <v>6845967</v>
+        <v>6845711</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6198,10 +6193,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123401802</v>
+        <v>123407757</v>
       </c>
       <c r="B54" t="n">
-        <v>57503</v>
+        <v>78517</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6214,39 +6209,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>396262</v>
+        <v>396169</v>
       </c>
       <c r="R54" t="n">
-        <v>6845711</v>
+        <v>6845665</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6293,22 +6283,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123407757</v>
+        <v>123404249</v>
       </c>
       <c r="B55" t="n">
-        <v>78517</v>
+        <v>78165</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6321,21 +6311,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6345,10 +6335,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>396169</v>
+        <v>396055</v>
       </c>
       <c r="R55" t="n">
-        <v>6845665</v>
+        <v>6846069</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6400,17 +6390,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123404249</v>
+        <v>123403156</v>
       </c>
       <c r="B56" t="n">
-        <v>78165</v>
+        <v>78517</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6423,37 +6413,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>396055</v>
+        <v>396197</v>
       </c>
       <c r="R56" t="n">
-        <v>6846069</v>
+        <v>6845889</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6480,9 +6470,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6497,22 +6497,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Malte Lindberg</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123403156</v>
+        <v>123407791</v>
       </c>
       <c r="B57" t="n">
-        <v>78517</v>
+        <v>80734</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>396197</v>
+        <v>396200</v>
       </c>
       <c r="R57" t="n">
-        <v>6845889</v>
+        <v>6845827</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6621,10 +6621,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123406080</v>
+        <v>123403609</v>
       </c>
       <c r="B58" t="n">
-        <v>57487</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6633,43 +6633,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>396199</v>
+        <v>396188</v>
       </c>
       <c r="R58" t="n">
-        <v>6846035</v>
+        <v>6845970</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6716,22 +6711,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123407791</v>
+        <v>123402230</v>
       </c>
       <c r="B59" t="n">
-        <v>80734</v>
+        <v>57487</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6744,37 +6739,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>396200</v>
+        <v>396288</v>
       </c>
       <c r="R59" t="n">
-        <v>6845827</v>
+        <v>6845740</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6801,19 +6801,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6828,22 +6818,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123403609</v>
+        <v>123404505</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>8445</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6856,21 +6846,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6880,10 +6870,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>396188</v>
+        <v>396090</v>
       </c>
       <c r="R60" t="n">
-        <v>6845970</v>
+        <v>6845976</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6942,10 +6932,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123402230</v>
+        <v>123407487</v>
       </c>
       <c r="B61" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6958,39 +6948,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>396288</v>
+        <v>396196</v>
       </c>
       <c r="R61" t="n">
-        <v>6845740</v>
+        <v>6845788</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7049,10 +7034,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123404505</v>
+        <v>123403633</v>
       </c>
       <c r="B62" t="n">
-        <v>8445</v>
+        <v>78876</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7061,41 +7046,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>396090</v>
+        <v>396198</v>
       </c>
       <c r="R62" t="n">
-        <v>6845976</v>
+        <v>6845932</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7122,9 +7121,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7139,22 +7148,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123407487</v>
+        <v>123406836</v>
       </c>
       <c r="B63" t="n">
-        <v>78518</v>
+        <v>78426</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7167,34 +7176,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>396196</v>
+        <v>396176</v>
       </c>
       <c r="R63" t="n">
-        <v>6845788</v>
+        <v>6845908</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7241,22 +7250,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123406836</v>
+        <v>123402056</v>
       </c>
       <c r="B64" t="n">
-        <v>78426</v>
+        <v>77709</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7269,34 +7278,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>396176</v>
+        <v>396287</v>
       </c>
       <c r="R64" t="n">
-        <v>6845908</v>
+        <v>6845734</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7355,10 +7364,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123402056</v>
+        <v>123407461</v>
       </c>
       <c r="B65" t="n">
-        <v>77709</v>
+        <v>79399</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7371,34 +7380,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>396287</v>
+        <v>396084</v>
       </c>
       <c r="R65" t="n">
-        <v>6845734</v>
+        <v>6845730</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7457,10 +7466,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123407461</v>
+        <v>123407465</v>
       </c>
       <c r="B66" t="n">
-        <v>79399</v>
+        <v>78517</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7473,34 +7482,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>396084</v>
+        <v>396196</v>
       </c>
       <c r="R66" t="n">
-        <v>6845730</v>
+        <v>6845788</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7547,22 +7556,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123407465</v>
+        <v>123407557</v>
       </c>
       <c r="B67" t="n">
-        <v>78517</v>
+        <v>57487</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7575,37 +7584,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>396196</v>
+        <v>396092</v>
       </c>
       <c r="R67" t="n">
-        <v>6845788</v>
+        <v>6845720</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7649,22 +7663,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123407557</v>
+        <v>123403974</v>
       </c>
       <c r="B68" t="n">
-        <v>57487</v>
+        <v>78518</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7677,42 +7691,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>396092</v>
+        <v>396139</v>
       </c>
       <c r="R68" t="n">
-        <v>6845720</v>
+        <v>6846046</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7768,10 +7777,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123403974</v>
+        <v>123402235</v>
       </c>
       <c r="B69" t="n">
-        <v>78518</v>
+        <v>57487</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7784,37 +7793,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>396139</v>
+        <v>396281</v>
       </c>
       <c r="R69" t="n">
-        <v>6846046</v>
+        <v>6845766</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7841,9 +7855,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7858,22 +7882,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123403633</v>
+        <v>123403126</v>
       </c>
       <c r="B70" t="n">
-        <v>78876</v>
+        <v>79399</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7886,51 +7910,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>396198</v>
+        <v>396200</v>
       </c>
       <c r="R70" t="n">
-        <v>6845932</v>
+        <v>6845919</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7957,19 +7967,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7984,22 +7984,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123403126</v>
+        <v>123403765</v>
       </c>
       <c r="B71" t="n">
-        <v>79399</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8008,41 +8008,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>396200</v>
+        <v>396203</v>
       </c>
       <c r="R71" t="n">
-        <v>6845919</v>
+        <v>6845971</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8069,9 +8069,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8086,22 +8096,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123403765</v>
+        <v>123403664</v>
       </c>
       <c r="B72" t="n">
-        <v>79891</v>
+        <v>78426</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8110,25 +8120,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8138,10 +8148,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>396203</v>
+        <v>396219</v>
       </c>
       <c r="R72" t="n">
-        <v>6845971</v>
+        <v>6845946</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -8173,7 +8183,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8183,7 +8193,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8210,10 +8220,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123402235</v>
+        <v>123403244</v>
       </c>
       <c r="B73" t="n">
-        <v>57487</v>
+        <v>79399</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8226,42 +8236,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>396281</v>
+        <v>396237</v>
       </c>
       <c r="R73" t="n">
-        <v>6845766</v>
+        <v>6845920</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8288,19 +8293,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8315,22 +8310,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123403664</v>
+        <v>123406803</v>
       </c>
       <c r="B74" t="n">
-        <v>78426</v>
+        <v>57487</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8343,37 +8338,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>396219</v>
+        <v>396156</v>
       </c>
       <c r="R74" t="n">
-        <v>6845946</v>
+        <v>6845922</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8400,19 +8400,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8427,22 +8417,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123403244</v>
+        <v>123407180</v>
       </c>
       <c r="B75" t="n">
-        <v>79399</v>
+        <v>78426</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8455,34 +8445,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>396237</v>
+        <v>396140</v>
       </c>
       <c r="R75" t="n">
-        <v>6845920</v>
+        <v>6845732</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8529,22 +8519,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123407180</v>
+        <v>123407564</v>
       </c>
       <c r="B76" t="n">
-        <v>78426</v>
+        <v>91003</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8557,37 +8547,46 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>396140</v>
+        <v>396154</v>
       </c>
       <c r="R76" t="n">
-        <v>6845732</v>
+        <v>6845889</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8614,9 +8613,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8631,19 +8640,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123407564</v>
+        <v>123406704</v>
       </c>
       <c r="B77" t="n">
         <v>91003</v>
@@ -8676,29 +8685,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>396154</v>
+        <v>396147</v>
       </c>
       <c r="R77" t="n">
-        <v>6845889</v>
+        <v>6845922</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8725,19 +8725,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8752,22 +8742,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123406704</v>
+        <v>123403734</v>
       </c>
       <c r="B78" t="n">
-        <v>91003</v>
+        <v>79399</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8780,21 +8770,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8804,10 +8794,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>396147</v>
+        <v>396152</v>
       </c>
       <c r="R78" t="n">
-        <v>6845922</v>
+        <v>6845999</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8866,10 +8856,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123403734</v>
+        <v>123406999</v>
       </c>
       <c r="B79" t="n">
-        <v>79399</v>
+        <v>78518</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8882,21 +8872,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8906,10 +8896,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396152</v>
+        <v>396169</v>
       </c>
       <c r="R79" t="n">
-        <v>6845999</v>
+        <v>6845810</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8968,10 +8958,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123406999</v>
+        <v>123407480</v>
       </c>
       <c r="B80" t="n">
-        <v>78518</v>
+        <v>79399</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8984,37 +8974,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>396169</v>
+        <v>396183</v>
       </c>
       <c r="R80" t="n">
-        <v>6845810</v>
+        <v>6845919</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9041,9 +9031,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9058,22 +9058,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123407480</v>
+        <v>123406774</v>
       </c>
       <c r="B81" t="n">
-        <v>79399</v>
+        <v>57487</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9086,37 +9086,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>396183</v>
+        <v>396147</v>
       </c>
       <c r="R81" t="n">
-        <v>6845919</v>
+        <v>6845918</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9143,19 +9148,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9170,22 +9165,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123406774</v>
+        <v>123403728</v>
       </c>
       <c r="B82" t="n">
-        <v>57487</v>
+        <v>78426</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9198,39 +9193,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>396147</v>
+        <v>396152</v>
       </c>
       <c r="R82" t="n">
-        <v>6845918</v>
+        <v>6845999</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,19 +9267,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123403728</v>
+        <v>123402952</v>
       </c>
       <c r="B83" t="n">
         <v>78426</v>
@@ -9325,17 +9315,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>396152</v>
+        <v>396193</v>
       </c>
       <c r="R83" t="n">
-        <v>6845999</v>
+        <v>6845821</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9362,9 +9352,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9379,22 +9379,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123402952</v>
+        <v>123407258</v>
       </c>
       <c r="B84" t="n">
-        <v>78426</v>
+        <v>79399</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9407,21 +9407,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>396193</v>
+        <v>396137</v>
       </c>
       <c r="R84" t="n">
-        <v>6845821</v>
+        <v>6845971</v>
       </c>
       <c r="S84" t="n">
         <v>4</v>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,10 +9503,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123407258</v>
+        <v>123403874</v>
       </c>
       <c r="B85" t="n">
-        <v>79399</v>
+        <v>78518</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9519,37 +9519,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>396137</v>
+        <v>396129</v>
       </c>
       <c r="R85" t="n">
-        <v>6845971</v>
+        <v>6846036</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9576,19 +9576,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9603,22 +9593,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123403874</v>
+        <v>123403073</v>
       </c>
       <c r="B86" t="n">
-        <v>78518</v>
+        <v>57640</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9631,37 +9621,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>396129</v>
+        <v>396190</v>
       </c>
       <c r="R86" t="n">
-        <v>6846036</v>
+        <v>6845863</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9688,9 +9687,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9705,22 +9714,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123403073</v>
+        <v>123406080</v>
       </c>
       <c r="B87" t="n">
-        <v>57640</v>
+        <v>57487</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9733,46 +9742,45 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>396190</v>
+        <v>396199</v>
       </c>
       <c r="R87" t="n">
-        <v>6845863</v>
+        <v>6846035</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9799,19 +9807,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:32</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Troligt tretåig hackspett och spillkråka.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,12 +9829,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -13176,10 +13179,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123401886</v>
+        <v>123399598</v>
       </c>
       <c r="B118" t="n">
-        <v>79399</v>
+        <v>78517</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13192,21 +13195,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13216,10 +13219,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>396474</v>
+        <v>396640</v>
       </c>
       <c r="R118" t="n">
-        <v>6845113</v>
+        <v>6845024</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13251,7 +13254,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13261,7 +13264,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13288,10 +13291,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123399598</v>
+        <v>123399779</v>
       </c>
       <c r="B119" t="n">
-        <v>78517</v>
+        <v>57487</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13304,37 +13307,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>396640</v>
+        <v>396519</v>
       </c>
       <c r="R119" t="n">
-        <v>6845024</v>
+        <v>6845294</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13361,19 +13369,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13388,22 +13386,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123399779</v>
+        <v>123401886</v>
       </c>
       <c r="B120" t="n">
-        <v>57487</v>
+        <v>79399</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13416,42 +13414,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>396519</v>
+        <v>396474</v>
       </c>
       <c r="R120" t="n">
-        <v>6845294</v>
+        <v>6845113</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13478,9 +13471,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13495,12 +13498,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13731,10 +13734,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123408781</v>
+        <v>123402421</v>
       </c>
       <c r="B123" t="n">
-        <v>79370</v>
+        <v>79399</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13747,21 +13750,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13771,13 +13774,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>396550</v>
+        <v>396519</v>
       </c>
       <c r="R123" t="n">
-        <v>6845271</v>
+        <v>6845160</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13804,9 +13807,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13821,22 +13834,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123402421</v>
+        <v>123408781</v>
       </c>
       <c r="B124" t="n">
-        <v>79399</v>
+        <v>79370</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13849,21 +13862,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13873,13 +13886,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>396519</v>
+        <v>396550</v>
       </c>
       <c r="R124" t="n">
-        <v>6845160</v>
+        <v>6845271</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13906,19 +13919,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13933,12 +13936,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14388,10 +14391,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>123385567</v>
+        <v>123379451</v>
       </c>
       <c r="B129" t="n">
-        <v>79370</v>
+        <v>79399</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14404,37 +14407,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>396806</v>
+        <v>396819</v>
       </c>
       <c r="R129" t="n">
-        <v>6845386</v>
+        <v>6844919</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14461,9 +14464,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14478,19 +14491,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>123379451</v>
+        <v>123377850</v>
       </c>
       <c r="B130" t="n">
         <v>79399</v>
@@ -14524,16 +14537,23 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>396819</v>
+        <v>396726</v>
       </c>
       <c r="R130" t="n">
-        <v>6844919</v>
+        <v>6845127</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
@@ -14565,7 +14585,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14575,7 +14595,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14584,6 +14604,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14595,17 +14616,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>123377850</v>
+        <v>123385567</v>
       </c>
       <c r="B131" t="n">
-        <v>79399</v>
+        <v>79370</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14618,44 +14639,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>396726</v>
+        <v>396806</v>
       </c>
       <c r="R131" t="n">
-        <v>6845127</v>
+        <v>6845386</v>
       </c>
       <c r="S131" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14682,40 +14696,29 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>

--- a/artfynd/A 6679-2025 artfynd.xlsx
+++ b/artfynd/A 6679-2025 artfynd.xlsx
@@ -4924,10 +4924,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123408392</v>
+        <v>123403134</v>
       </c>
       <c r="B42" t="n">
-        <v>79399</v>
+        <v>78426</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4940,34 +4940,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396264</v>
+        <v>396200</v>
       </c>
       <c r="R42" t="n">
-        <v>6845661</v>
+        <v>6845887</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5138,10 +5138,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123403134</v>
+        <v>123408392</v>
       </c>
       <c r="B44" t="n">
-        <v>78426</v>
+        <v>79399</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5154,34 +5154,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396200</v>
+        <v>396264</v>
       </c>
       <c r="R44" t="n">
-        <v>6845887</v>
+        <v>6845661</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5872,10 +5872,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123408154</v>
+        <v>123401802</v>
       </c>
       <c r="B51" t="n">
-        <v>78517</v>
+        <v>57503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5888,37 +5888,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>396218</v>
+        <v>396262</v>
       </c>
       <c r="R51" t="n">
-        <v>6845772</v>
+        <v>6845711</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5945,19 +5950,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5972,22 +5967,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123403759</v>
+        <v>123408154</v>
       </c>
       <c r="B52" t="n">
-        <v>79370</v>
+        <v>78517</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6000,37 +5995,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>396263</v>
+        <v>396218</v>
       </c>
       <c r="R52" t="n">
-        <v>6845967</v>
+        <v>6845772</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6057,9 +6052,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6074,22 +6079,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123401802</v>
+        <v>123403759</v>
       </c>
       <c r="B53" t="n">
-        <v>57503</v>
+        <v>79370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6102,39 +6107,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>396262</v>
+        <v>396263</v>
       </c>
       <c r="R53" t="n">
-        <v>6845711</v>
+        <v>6845967</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123407757</v>
+        <v>123407791</v>
       </c>
       <c r="B54" t="n">
-        <v>78517</v>
+        <v>80734</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6209,37 +6209,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>396169</v>
+        <v>396200</v>
       </c>
       <c r="R54" t="n">
-        <v>6845665</v>
+        <v>6845827</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6266,9 +6266,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6283,22 +6293,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123404249</v>
+        <v>123403609</v>
       </c>
       <c r="B55" t="n">
-        <v>78165</v>
+        <v>79891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6307,25 +6317,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6335,10 +6345,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>396055</v>
+        <v>396188</v>
       </c>
       <c r="R55" t="n">
-        <v>6846069</v>
+        <v>6845970</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,14 +6400,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123403156</v>
+        <v>123407757</v>
       </c>
       <c r="B56" t="n">
         <v>78517</v>
@@ -6433,17 +6443,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>396197</v>
+        <v>396169</v>
       </c>
       <c r="R56" t="n">
-        <v>6845889</v>
+        <v>6845665</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6470,19 +6480,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6497,22 +6497,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123407791</v>
+        <v>123404249</v>
       </c>
       <c r="B57" t="n">
-        <v>80734</v>
+        <v>78165</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6525,37 +6525,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>396200</v>
+        <v>396055</v>
       </c>
       <c r="R57" t="n">
-        <v>6845827</v>
+        <v>6846069</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6582,19 +6582,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6609,22 +6599,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123403609</v>
+        <v>123403156</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>78517</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6633,41 +6623,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>396188</v>
+        <v>396197</v>
       </c>
       <c r="R58" t="n">
-        <v>6845970</v>
+        <v>6845889</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6694,9 +6684,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6711,12 +6711,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -8754,10 +8754,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123403734</v>
+        <v>123406999</v>
       </c>
       <c r="B78" t="n">
-        <v>79399</v>
+        <v>78518</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8770,21 +8770,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>396152</v>
+        <v>396169</v>
       </c>
       <c r="R78" t="n">
-        <v>6845999</v>
+        <v>6845810</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8856,10 +8856,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123406999</v>
+        <v>123403734</v>
       </c>
       <c r="B79" t="n">
-        <v>78518</v>
+        <v>79399</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8872,21 +8872,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396169</v>
+        <v>396152</v>
       </c>
       <c r="R79" t="n">
-        <v>6845810</v>
+        <v>6845999</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -13734,10 +13734,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123402421</v>
+        <v>123408781</v>
       </c>
       <c r="B123" t="n">
-        <v>79399</v>
+        <v>79370</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13750,21 +13750,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13774,13 +13774,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>396519</v>
+        <v>396550</v>
       </c>
       <c r="R123" t="n">
-        <v>6845160</v>
+        <v>6845271</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13807,19 +13807,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13834,22 +13824,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123408781</v>
+        <v>123402421</v>
       </c>
       <c r="B124" t="n">
-        <v>79370</v>
+        <v>79399</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13862,21 +13852,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13886,13 +13876,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>396550</v>
+        <v>396519</v>
       </c>
       <c r="R124" t="n">
-        <v>6845271</v>
+        <v>6845160</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13919,9 +13909,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13936,12 +13936,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14391,10 +14391,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>123379451</v>
+        <v>123385567</v>
       </c>
       <c r="B129" t="n">
-        <v>79399</v>
+        <v>79370</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14407,37 +14407,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>396819</v>
+        <v>396806</v>
       </c>
       <c r="R129" t="n">
-        <v>6844919</v>
+        <v>6845386</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14464,19 +14464,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14491,19 +14481,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>123377850</v>
+        <v>123379451</v>
       </c>
       <c r="B130" t="n">
         <v>79399</v>
@@ -14537,23 +14527,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>396726</v>
+        <v>396819</v>
       </c>
       <c r="R130" t="n">
-        <v>6845127</v>
+        <v>6844919</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
@@ -14585,7 +14568,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14595,7 +14578,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14604,7 +14587,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14616,17 +14598,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>123385567</v>
+        <v>123377850</v>
       </c>
       <c r="B131" t="n">
-        <v>79370</v>
+        <v>79399</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14639,37 +14621,44 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>396806</v>
+        <v>396726</v>
       </c>
       <c r="R131" t="n">
-        <v>6845386</v>
+        <v>6845127</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14696,29 +14685,40 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -17717,10 +17717,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>123380521</v>
+        <v>123380545</v>
       </c>
       <c r="B159" t="n">
-        <v>57503</v>
+        <v>79370</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17733,42 +17733,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>396848</v>
+        <v>396850</v>
       </c>
       <c r="R159" t="n">
-        <v>6845171</v>
+        <v>6845163</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17795,9 +17790,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17812,22 +17817,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>123380545</v>
+        <v>123380521</v>
       </c>
       <c r="B160" t="n">
-        <v>79370</v>
+        <v>57503</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17840,37 +17845,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>396850</v>
+        <v>396848</v>
       </c>
       <c r="R160" t="n">
-        <v>6845163</v>
+        <v>6845171</v>
       </c>
       <c r="S160" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17897,19 +17907,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17924,12 +17924,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 6679-2025 artfynd.xlsx
+++ b/artfynd/A 6679-2025 artfynd.xlsx
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123403123</v>
+        <v>123403073</v>
       </c>
       <c r="B5" t="n">
-        <v>78433</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,37 +1017,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396200</v>
+        <v>396190</v>
       </c>
       <c r="R5" t="n">
-        <v>6845919</v>
+        <v>6845863</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,9 +1083,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1110,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123404513</v>
+        <v>123404624</v>
       </c>
       <c r="B6" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396090</v>
+        <v>396107</v>
       </c>
       <c r="R6" t="n">
-        <v>6845976</v>
+        <v>6845974</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123406774</v>
+        <v>123403123</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>78433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,39 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396147</v>
+        <v>396200</v>
       </c>
       <c r="R7" t="n">
-        <v>6845918</v>
+        <v>6845919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,22 +1314,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123403073</v>
+        <v>123404513</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>78433</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,46 +1342,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396190</v>
+        <v>396090</v>
       </c>
       <c r="R8" t="n">
-        <v>6845863</v>
+        <v>6845976</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,19 +1399,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,22 +1416,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123404624</v>
+        <v>123406774</v>
       </c>
       <c r="B9" t="n">
-        <v>78525</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,34 +1444,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396107</v>
+        <v>396147</v>
       </c>
       <c r="R9" t="n">
-        <v>6845974</v>
+        <v>6845918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,12 +1523,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123407713</v>
+        <v>123407967</v>
       </c>
       <c r="B30" t="n">
-        <v>79377</v>
+        <v>79406</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3670,37 +3670,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>396195</v>
+        <v>396252</v>
       </c>
       <c r="R30" t="n">
-        <v>6845835</v>
+        <v>6845578</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,19 +3727,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3754,19 +3744,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123407967</v>
+        <v>123403244</v>
       </c>
       <c r="B31" t="n">
         <v>79406</v>
@@ -3802,14 +3792,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>396252</v>
+        <v>396237</v>
       </c>
       <c r="R31" t="n">
-        <v>6845578</v>
+        <v>6845920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,19 +3846,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123403244</v>
+        <v>123407763</v>
       </c>
       <c r="B32" t="n">
         <v>79406</v>
@@ -3904,14 +3894,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396237</v>
+        <v>396169</v>
       </c>
       <c r="R32" t="n">
-        <v>6845920</v>
+        <v>6845665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3958,22 +3948,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123407763</v>
+        <v>123406803</v>
       </c>
       <c r="B33" t="n">
-        <v>79406</v>
+        <v>57491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3986,34 +3976,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>396169</v>
+        <v>396156</v>
       </c>
       <c r="R33" t="n">
-        <v>6845665</v>
+        <v>6845922</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,22 +4055,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123406803</v>
+        <v>123402069</v>
       </c>
       <c r="B34" t="n">
-        <v>57491</v>
+        <v>80741</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4088,39 +4083,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396156</v>
+        <v>396287</v>
       </c>
       <c r="R34" t="n">
-        <v>6845922</v>
+        <v>6845734</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,22 +4157,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123402069</v>
+        <v>123407713</v>
       </c>
       <c r="B35" t="n">
-        <v>80741</v>
+        <v>79377</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,37 +4185,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396287</v>
+        <v>396195</v>
       </c>
       <c r="R35" t="n">
-        <v>6845734</v>
+        <v>6845835</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4252,9 +4242,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,12 +4269,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123404249</v>
+        <v>123404505</v>
       </c>
       <c r="B41" t="n">
-        <v>78172</v>
+        <v>8447</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,25 +4823,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396055</v>
+        <v>396090</v>
       </c>
       <c r="R41" t="n">
-        <v>6846069</v>
+        <v>6845976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4906,17 +4906,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123403734</v>
+        <v>123404249</v>
       </c>
       <c r="B42" t="n">
-        <v>79406</v>
+        <v>78172</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396152</v>
+        <v>396055</v>
       </c>
       <c r="R42" t="n">
-        <v>6845999</v>
+        <v>6846069</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5008,17 +5008,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123404505</v>
+        <v>123403734</v>
       </c>
       <c r="B43" t="n">
-        <v>8447</v>
+        <v>79406</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5027,25 +5027,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396090</v>
+        <v>396152</v>
       </c>
       <c r="R43" t="n">
-        <v>6845976</v>
+        <v>6845999</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123402952</v>
+        <v>123406999</v>
       </c>
       <c r="B46" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5337,37 +5337,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396193</v>
+        <v>396169</v>
       </c>
       <c r="R46" t="n">
-        <v>6845821</v>
+        <v>6845810</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5394,19 +5394,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,22 +5411,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123403134</v>
+        <v>123403874</v>
       </c>
       <c r="B47" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5449,37 +5439,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396200</v>
+        <v>396129</v>
       </c>
       <c r="R47" t="n">
-        <v>6845887</v>
+        <v>6846036</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5506,19 +5496,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5533,22 +5513,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123406999</v>
+        <v>123402952</v>
       </c>
       <c r="B48" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5561,37 +5541,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396169</v>
+        <v>396193</v>
       </c>
       <c r="R48" t="n">
-        <v>6845810</v>
+        <v>6845821</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5618,9 +5598,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,22 +5625,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123403874</v>
+        <v>123403134</v>
       </c>
       <c r="B49" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5663,37 +5653,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Glitjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>396129</v>
+        <v>396200</v>
       </c>
       <c r="R49" t="n">
-        <v>6846036</v>
+        <v>6845887</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5720,9 +5710,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5737,12 +5737,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6896,10 +6896,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123402432</v>
+        <v>123403054</v>
       </c>
       <c r="B61" t="n">
-        <v>80741</v>
+        <v>78433</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6912,34 +6912,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>396300</v>
+        <v>396190</v>
       </c>
       <c r="R61" t="n">
-        <v>6845775</v>
+        <v>6845863</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7008,10 +7008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123401802</v>
+        <v>123403633</v>
       </c>
       <c r="B62" t="n">
-        <v>57507</v>
+        <v>78883</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7024,42 +7024,51 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>396262</v>
+        <v>396198</v>
       </c>
       <c r="R62" t="n">
-        <v>6845711</v>
+        <v>6845932</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7086,9 +7095,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7103,22 +7122,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123402545</v>
+        <v>123408154</v>
       </c>
       <c r="B63" t="n">
-        <v>57644</v>
+        <v>78524</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7131,43 +7150,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>396287</v>
+        <v>396218</v>
       </c>
       <c r="R63" t="n">
-        <v>6845788</v>
+        <v>6845772</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7199,7 +7209,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7209,7 +7219,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7236,10 +7246,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123403054</v>
+        <v>123402545</v>
       </c>
       <c r="B64" t="n">
-        <v>78433</v>
+        <v>57644</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7252,34 +7262,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>396190</v>
+        <v>396287</v>
       </c>
       <c r="R64" t="n">
-        <v>6845863</v>
+        <v>6845788</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7311,7 +7330,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7321,7 +7340,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7348,10 +7367,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123403633</v>
+        <v>123402432</v>
       </c>
       <c r="B65" t="n">
-        <v>78883</v>
+        <v>80741</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7364,48 +7383,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>967</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>396198</v>
+        <v>396300</v>
       </c>
       <c r="R65" t="n">
-        <v>6845932</v>
+        <v>6845775</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7437,7 +7442,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7447,7 +7452,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7474,10 +7479,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123408154</v>
+        <v>123401802</v>
       </c>
       <c r="B66" t="n">
-        <v>78524</v>
+        <v>57507</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7490,37 +7495,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Grästjärnen, Grästjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>396218</v>
+        <v>396262</v>
       </c>
       <c r="R66" t="n">
-        <v>6845772</v>
+        <v>6845711</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7547,19 +7557,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7574,12 +7574,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123404225</v>
+        <v>123403156</v>
       </c>
       <c r="B72" t="n">
         <v>78524</v>
@@ -8162,17 +8162,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Grästjärnen, Dlr</t>
+          <t>Glitjärnen, Glitjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>396199</v>
+        <v>396197</v>
       </c>
       <c r="R72" t="n">
-        <v>6846035</v>
+        <v>6845889</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8199,9 +8199,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8216,19 +8226,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123403156</v>
+        <v>123404225</v>
       </c>
       <c r="B73" t="n">
         <v>78524</v>
@@ -8264,17 +8274,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Glitjärnen, Glitjärnen, Dlr</t>
+          <t>Grästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>396197</v>
+        <v>396199</v>
       </c>
       <c r="R73" t="n">
-        <v>6845889</v>
+        <v>6846035</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8301,19 +8311,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8328,12 +8328,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -10045,10 +10045,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123400661</v>
+        <v>123408311</v>
       </c>
       <c r="B90" t="n">
-        <v>79377</v>
+        <v>57491</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10061,37 +10061,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>396525</v>
+        <v>396431</v>
       </c>
       <c r="R90" t="n">
-        <v>6845326</v>
+        <v>6845432</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10118,19 +10123,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:34</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10145,22 +10140,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123408311</v>
+        <v>123400661</v>
       </c>
       <c r="B91" t="n">
-        <v>57491</v>
+        <v>79377</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10173,42 +10168,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>396431</v>
+        <v>396525</v>
       </c>
       <c r="R91" t="n">
-        <v>6845432</v>
+        <v>6845326</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10235,9 +10225,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10252,12 +10252,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>123379305</v>
+        <v>123378915</v>
       </c>
       <c r="B136" t="n">
-        <v>57491</v>
+        <v>78433</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15166,42 +15166,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>396758</v>
+        <v>396782</v>
       </c>
       <c r="R136" t="n">
-        <v>6844990</v>
+        <v>6845074</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15228,9 +15223,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15245,22 +15250,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>123378915</v>
+        <v>123379305</v>
       </c>
       <c r="B137" t="n">
-        <v>78433</v>
+        <v>57491</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15273,37 +15278,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>396782</v>
+        <v>396758</v>
       </c>
       <c r="R137" t="n">
-        <v>6845074</v>
+        <v>6844990</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15330,19 +15340,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15357,12 +15357,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -15583,10 +15583,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>123386610</v>
+        <v>123379787</v>
       </c>
       <c r="B140" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15599,37 +15599,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>396715</v>
+        <v>396858</v>
       </c>
       <c r="R140" t="n">
-        <v>6845143</v>
+        <v>6845010</v>
       </c>
       <c r="S140" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15656,19 +15656,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15683,22 +15673,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>123379787</v>
+        <v>123386610</v>
       </c>
       <c r="B141" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15711,37 +15701,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>396858</v>
+        <v>396715</v>
       </c>
       <c r="R141" t="n">
-        <v>6845010</v>
+        <v>6845143</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15768,9 +15758,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15785,12 +15785,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -17153,10 +17153,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>123384283</v>
+        <v>123381911</v>
       </c>
       <c r="B154" t="n">
-        <v>79406</v>
+        <v>78525</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17169,34 +17169,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>396987</v>
+        <v>397001</v>
       </c>
       <c r="R154" t="n">
-        <v>6845180</v>
+        <v>6845137</v>
       </c>
       <c r="S154" t="n">
         <v>4</v>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17265,10 +17265,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>123381911</v>
+        <v>123384283</v>
       </c>
       <c r="B155" t="n">
-        <v>78525</v>
+        <v>79406</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17281,34 +17281,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>397001</v>
+        <v>396987</v>
       </c>
       <c r="R155" t="n">
-        <v>6845137</v>
+        <v>6845180</v>
       </c>
       <c r="S155" t="n">
         <v>4</v>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17707,10 +17707,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>123380521</v>
+        <v>123385003</v>
       </c>
       <c r="B159" t="n">
-        <v>57507</v>
+        <v>78433</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17723,42 +17723,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>396848</v>
+        <v>396940</v>
       </c>
       <c r="R159" t="n">
-        <v>6845171</v>
+        <v>6845309</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17785,9 +17785,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17802,22 +17812,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>123385003</v>
+        <v>123380521</v>
       </c>
       <c r="B160" t="n">
-        <v>78433</v>
+        <v>57507</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17830,42 +17840,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>396940</v>
+        <v>396848</v>
       </c>
       <c r="R160" t="n">
-        <v>6845309</v>
+        <v>6845171</v>
       </c>
       <c r="S160" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17892,19 +17902,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>17:04</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17919,12 +17919,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -18043,10 +18043,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>123377962</v>
+        <v>123381093</v>
       </c>
       <c r="B162" t="n">
-        <v>79898</v>
+        <v>78525</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18055,40 +18055,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>396727</v>
+        <v>396919</v>
       </c>
       <c r="R162" t="n">
-        <v>6845110</v>
+        <v>6845236</v>
       </c>
       <c r="S162" t="n">
         <v>4</v>
@@ -18120,7 +18118,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18130,7 +18128,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18139,7 +18137,6 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -18151,17 +18148,17 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>123384079</v>
+        <v>123377962</v>
       </c>
       <c r="B163" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18170,38 +18167,40 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Jenstjärnen, Jenstjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>396977</v>
+        <v>396727</v>
       </c>
       <c r="R163" t="n">
-        <v>6845168</v>
+        <v>6845110</v>
       </c>
       <c r="S163" t="n">
         <v>4</v>
@@ -18233,7 +18232,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18243,7 +18242,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18252,6 +18251,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -18263,17 +18263,17 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Malte Lindberg, Håkan Thenander, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>123384371</v>
+        <v>123384079</v>
       </c>
       <c r="B164" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18286,21 +18286,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18310,10 +18310,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>396967</v>
+        <v>396977</v>
       </c>
       <c r="R164" t="n">
-        <v>6845183</v>
+        <v>6845168</v>
       </c>
       <c r="S164" t="n">
         <v>4</v>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18382,10 +18382,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>123384489</v>
+        <v>123384371</v>
       </c>
       <c r="B165" t="n">
-        <v>78524</v>
+        <v>79406</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18398,21 +18398,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18422,10 +18422,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>396985</v>
+        <v>396967</v>
       </c>
       <c r="R165" t="n">
-        <v>6845187</v>
+        <v>6845183</v>
       </c>
       <c r="S165" t="n">
         <v>4</v>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18494,10 +18494,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>123381093</v>
+        <v>123384489</v>
       </c>
       <c r="B166" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18510,21 +18510,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18534,10 +18534,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>396919</v>
+        <v>396985</v>
       </c>
       <c r="R166" t="n">
-        <v>6845236</v>
+        <v>6845187</v>
       </c>
       <c r="S166" t="n">
         <v>4</v>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18835,7 +18835,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>123381981</v>
+        <v>123385250</v>
       </c>
       <c r="B169" t="n">
         <v>79406</v>
@@ -18871,17 +18871,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Slaktar-Johantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>396988</v>
+        <v>396864</v>
       </c>
       <c r="R169" t="n">
-        <v>6845143</v>
+        <v>6845294</v>
       </c>
       <c r="S169" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18908,19 +18908,9 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>15:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18935,19 +18925,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>123385250</v>
+        <v>123381981</v>
       </c>
       <c r="B170" t="n">
         <v>79406</v>
@@ -18983,17 +18973,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Slaktar-Johantjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>396864</v>
+        <v>396988</v>
       </c>
       <c r="R170" t="n">
-        <v>6845294</v>
+        <v>6845143</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19020,9 +19010,19 @@
           <t>2025-03-22</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19037,12 +19037,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -19273,7 +19273,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>123382029</v>
+        <v>123382835</v>
       </c>
       <c r="B173" t="n">
         <v>79406</v>
@@ -19309,17 +19309,17 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>397016</v>
+        <v>397010</v>
       </c>
       <c r="R173" t="n">
-        <v>6845132</v>
+        <v>6845133</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19373,22 +19373,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
+          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>123382835</v>
+        <v>123379411</v>
       </c>
       <c r="B174" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19401,21 +19401,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19425,10 +19425,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>397010</v>
+        <v>396819</v>
       </c>
       <c r="R174" t="n">
-        <v>6845133</v>
+        <v>6844919</v>
       </c>
       <c r="S174" t="n">
         <v>4</v>
@@ -19460,7 +19460,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19470,7 +19470,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19497,10 +19497,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>123379411</v>
+        <v>123382029</v>
       </c>
       <c r="B175" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19513,37 +19513,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Stentjärnen, Stentjärnen, Dlr</t>
+          <t>Stentjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>396819</v>
+        <v>397016</v>
       </c>
       <c r="R175" t="n">
-        <v>6844919</v>
+        <v>6845132</v>
       </c>
       <c r="S175" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19597,12 +19597,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Lars-Erik Nilsson, Håkan Thenander</t>
+          <t>Lars-Erik Nilsson, Håkan Thenander, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>

--- a/artfynd/A 6679-2025 artfynd.xlsx
+++ b/artfynd/A 6679-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY199"/>
+  <dimension ref="A1:AZ199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123401136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402952</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403054</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403134</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403664</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403728</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404309</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404513</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406112</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406836</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1983,6 +2048,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407180</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407639</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408217</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403633</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402069</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2522,6 +2612,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402432</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,6 +2724,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407791</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2745,6 +2845,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123405701</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2842,6 +2947,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406704</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2958,6 +3068,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407564</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3055,6 +3170,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404079</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3152,6 +3272,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407801</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3249,6 +3374,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403119</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3346,6 +3476,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403866</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3443,6 +3578,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404249</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3540,6 +3680,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407419</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3647,6 +3792,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403156</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3744,6 +3894,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404225</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3841,6 +3996,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404524</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3938,6 +4098,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406540</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4035,6 +4200,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407465</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4132,6 +4302,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407626</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4229,6 +4404,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407757</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4336,6 +4516,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407949</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4433,6 +4618,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408056</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4540,6 +4730,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408121</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4647,6 +4842,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408154</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4754,6 +4954,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408514</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4851,6 +5056,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123401152</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4958,6 +5168,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123401667</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5055,6 +5270,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402278</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5152,6 +5372,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403126</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5259,6 +5484,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403202</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5356,6 +5586,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403244</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5463,6 +5698,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403637</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5560,6 +5800,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403734</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5657,6 +5902,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404391</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5764,6 +6014,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406165</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5861,6 +6116,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406473</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5968,6 +6228,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407258</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6065,6 +6330,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407461</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6172,6 +6442,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407480</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6279,6 +6554,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407585</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6376,6 +6656,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407661</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6473,6 +6758,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407763</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6570,6 +6860,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407967</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6667,6 +6962,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408077</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6774,6 +7074,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408392</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6881,6 +7186,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408539</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6978,6 +7288,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403609</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7085,6 +7400,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403765</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7182,6 +7502,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402056</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7279,6 +7604,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402921</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7376,6 +7706,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403854</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7478,6 +7813,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123401802</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7580,6 +7920,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402929</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7682,6 +8027,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402230</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7794,6 +8144,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402235</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7896,6 +8251,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402307</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7998,6 +8358,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123405032</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8108,6 +8473,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406080</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8218,6 +8588,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406592</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8320,6 +8695,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406774</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8425,6 +8805,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407242</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8527,6 +8912,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407519</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8629,6 +9019,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407557</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8741,6 +9136,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407432</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8857,6 +9257,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402545</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8973,6 +9378,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403073</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9075,6 +9485,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404072</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9172,6 +9587,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404505</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9269,6 +9689,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402477</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9366,6 +9791,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403761</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9463,6 +9893,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403874</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9560,6 +9995,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403974</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9657,6 +10097,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404245</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9754,6 +10199,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404624</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9851,6 +10301,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406999</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9958,6 +10413,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407113</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10065,6 +10525,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407471</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10162,6 +10627,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407487</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10259,6 +10729,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407642</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10366,6 +10841,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408527</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10463,6 +10943,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402042</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10560,6 +11045,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403759</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10667,6 +11157,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407713</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10764,6 +11259,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407295</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10861,6 +11361,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407803</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10958,6 +11463,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408525</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11055,6 +11565,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408313</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11152,6 +11667,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408505</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11249,6 +11769,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399686</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11351,6 +11876,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408311</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11458,6 +11988,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399844</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11555,6 +12090,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408293</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11662,6 +12202,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399827</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11769,6 +12314,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406963</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11876,6 +12426,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403994</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11983,6 +12538,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404671</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12092,6 +12652,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123425743</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12199,6 +12764,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404007</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12311,6 +12881,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404256</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12418,6 +12993,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123404427</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12525,6 +13105,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374718</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12640,6 +13225,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123376254</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12750,6 +13340,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123376924</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12856,6 +13451,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123376553</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12953,6 +13553,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399403</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13070,6 +13675,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123400140</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13177,6 +13787,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399598</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13284,6 +13899,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402396</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13396,6 +14016,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374624</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13503,6 +14128,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123376404</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13618,6 +14248,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123376759</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13728,6 +14363,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123376950</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13835,6 +14475,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399418</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13942,6 +14587,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123401144</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14049,6 +14699,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123401886</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14156,6 +14811,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402421</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14263,6 +14923,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403144</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14360,6 +15025,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377546</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14467,6 +15137,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402218</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14574,6 +15249,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403007</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14671,6 +15351,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408680</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14773,6 +15458,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399779</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14885,6 +15575,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123376713</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14997,6 +15692,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377228</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15099,6 +15799,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408728</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15206,6 +15911,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377557</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15303,6 +16013,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408781</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15410,6 +16125,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378809</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15517,6 +16237,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378915</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15624,6 +16349,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379157</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15731,6 +16461,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379411</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15843,6 +16578,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123380397</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15950,6 +16690,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384645</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16062,6 +16807,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385003</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16169,6 +16919,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123386610</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16270,6 +17025,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123390241</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16367,6 +17127,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384781</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16483,6 +17248,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123383301</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16590,6 +17360,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379369</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16697,6 +17472,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384079</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16794,6 +17574,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384240</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16901,6 +17686,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384388</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17008,6 +17798,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384489</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17105,6 +17900,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385270</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17220,6 +18020,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377850</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17327,6 +18132,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379008</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17434,6 +18244,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379451</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17541,6 +18356,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123381981</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17648,6 +18468,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123382029</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17755,6 +18580,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123382835</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17862,6 +18692,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384283</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17969,6 +18804,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384371</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18066,6 +18906,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385250</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18173,6 +19018,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385506</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18280,6 +19130,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385540</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18387,6 +19242,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123386516</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18497,6 +19357,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377943</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18607,6 +19472,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377962</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18714,6 +19584,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123380217</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18816,6 +19691,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123380073</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18918,6 +19798,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123380521</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19020,6 +19905,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123383085</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19122,6 +20012,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123386346</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19224,6 +20119,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379305</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19336,6 +20236,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385504</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19448,6 +20353,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123386532</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19560,6 +20470,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379657</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19667,6 +20582,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378194</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19764,6 +20684,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379787</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19871,6 +20796,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123381093</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19978,6 +20908,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123381911</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20085,6 +21020,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123381975</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20192,6 +21132,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384509</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20289,6 +21234,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123384879</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20386,6 +21336,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385225</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20493,6 +21448,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385391</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20600,6 +21560,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123380545</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20707,6 +21672,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123381657</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20804,6 +21774,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123382803</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20911,6 +21886,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123383009</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21018,6 +21998,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385408</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21115,6 +22100,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123385567</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21222,8 +22212,213 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123386383</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>